--- a/user_feedback_responses.xlsx
+++ b/user_feedback_responses.xlsx
@@ -417,8 +417,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="47" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -471,7 +471,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/24/2026 10:10:00</t>
+          <t>07/24/2026 10:52:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07/25/2026 00:50:00</t>
+          <t>07/25/2026 00:39:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/25/2026 14:47:00</t>
+          <t>07/25/2026 14:06:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/26/2026 04:18:00</t>
+          <t>07/26/2026 04:35:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/26/2026 18:45:00</t>
+          <t>07/26/2026 18:26:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/27/2026 08:30:00</t>
+          <t>07/27/2026 08:22:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/27/2026 22:14:00</t>
+          <t>07/27/2026 22:17:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -751,17 +751,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/28/2026 12:45:00</t>
+          <t>07/28/2026 12:33:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>Sam Martin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>sam.martin.dev@freelancehq.org</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -769,14 +769,12 @@
           <t>GBCUGYBTEEPXFBXH646LWKGITBIXEOI4ARJ55O4O5LBRRWVCDQLGXBPS</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E9" t="n">
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Multi-token selection with USDC and XLM is great. Would love to see EURC liquidity expanded.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -793,17 +791,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/29/2026 02:29:00</t>
+          <t>07/29/2026 02:52:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Bob Perez</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>bob.perez99@techsquad.dev</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -811,14 +809,12 @@
           <t>GCCSLS4KCKIAS3WZKYKOP4ZTR7T7SZNVU4IKJ7T5N76X7TMYPVMX2353</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
+      <c r="E10" t="n">
+        <v>5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Tested a 3-way split (40/30/30) with our backend and QA team. Remainder stroop was correctly sent to the last wallet.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -835,17 +831,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/29/2026 16:31:00</t>
+          <t>07/29/2026 16:24:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>Eva Garcia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>eva.garcia.design@creativepod.net</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -853,14 +849,12 @@
           <t>GBGBNRPDVADZCTY7LEJWNSMW4AZ2EOYCQSHH2MAKGLSYKIXAN4WAFO2P</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>v</t>
-        </is>
+      <c r="E11" t="n">
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Very clean dark-mode UI. Connecting Freighter wallet and switching network was instantaneous.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -877,17 +871,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/30/2026 06:19:00</t>
+          <t>07/30/2026 06:48:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>Ivy Perez</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>_</t>
+          <t>ivy.perez.ux@gmail.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -895,14 +889,12 @@
           <t>GALWAGUQDTJZD5WGCLYDY5HPPZJT4HMFDOAQWPNVJJPTCR6EOPRPMTSE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>v</t>
-        </is>
+      <c r="E12" t="n">
+        <v>4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>Adding automatic whitespace trimming on address inputs stopped me from getting invalid public key errors.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -919,17 +911,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/30/2026 20:45:00</t>
+          <t>07/30/2026 20:39:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>Ruby Anderson</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>ruby.anderson.lead@yahoo.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -937,14 +929,12 @@
           <t>GBCLAJMPGEFN7JULVJLJRCLAQBMSJX57CPJU47H4EHYFDDL5WGCV7BCA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
+      <c r="E13" t="n">
+        <v>5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>The share revision proposal feature is a game-changer for dynamic project milestone re-allocations.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -961,17 +951,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/31/2026 10:33:00</t>
+          <t>07/31/2026 10:42:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Alice Walker</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>alice.walker.ph@outlook.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -979,14 +969,12 @@
           <t>GBP7QK3HTCGOX5MOR7MXH44H5KI3V6PRR3EOHRRQNYIOZT7VXZIHWI4M</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
+      <c r="E14" t="n">
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>Tested from the Philippines and the real-time PHP fiat conversion gave me an accurate local value estimate.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1003,17 +991,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/01/2026 00:22:00</t>
+          <t>08/01/2026 00:38:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Charlie Garcia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>charlie.garcia.audits@proton.me</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1021,14 +1009,12 @@
           <t>GAK232LDEV27O5L76TRL6KIKG45EMNRQ3ASHVQOBXQVHSC6BSO3QNAO4</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
+      <c r="E15" t="n">
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>The PDF cryptographic receipt download is great for bookkeeping and submitting to our DAO accountant.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1045,17 +1031,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/01/2026 14:10:00</t>
+          <t>08/01/2026 14:11:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>Henry Jones</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>henry.jones.squad@icloud.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1063,14 +1049,12 @@
           <t>GCH6F4EBCYEYZYLQIXRVW55BN3CTLEIE547GILASFVMYWZMQTTFJTSYS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
+      <c r="E16" t="n">
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>Super fast finality compared to Ethereum multisigs. Payouts landed across all 3 team wallets in under 4 seconds.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1087,17 +1071,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/02/2026 04:13:00</t>
+          <t>08/02/2026 04:15:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Mia Wilson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>mia.wilson.artist@web3devs.io</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1105,14 +1089,12 @@
           <t>GBZVERAONGPDJEU7HUMDZYZ2RDYMMGAHJ4KREQMUVI5UQFOTBMKKXKZ4</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
+      <c r="E17" t="n">
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Love the 1-click presets (50/50, 60/40). Makes setting up recurring design splits effortless.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1129,17 +1111,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/02/2026 18:10:00</t>
+          <t>08/02/2026 18:12:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Carlos Mendez</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>carlos.mendez.mgmt@designcollective.co</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1147,14 +1129,12 @@
           <t>GDSDUP5S634ERPIEKVMJXLZL4WXE7ZGYS33GRC2AXCXYPYHZCT6AVLNB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E18" t="n">
+        <v>5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>The Hosted Invoice portal (/invoice/[id]) allowed our client to inspect itemized deliverables before funding.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1171,17 +1151,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/03/2026 08:54:00</t>
+          <t>08/03/2026 08:55:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Maya Lin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>maya.lin.frontend@freelancehq.org</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1189,14 +1169,12 @@
           <t>GDA5CL6G5XIWCIUBLVYUNI2XLRBI5WW7WOMC5BIGTAY3TXW62P67B4PA</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E19" t="n">
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>Pre-flight fee preview gives 100% confidence that no funds are lost to rounding issues.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1213,17 +1191,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/03/2026 22:44:00</t>
+          <t>08/03/2026 22:32:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>Lucas Silva</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>lucas.silva.mobile@techsquad.dev</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1231,14 +1209,12 @@
           <t>GCGC7RLNHYXGJYP3KAO4M3VUXHETXK7CQAEED5AZR7RPICLHWOCSK6GG</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
+      <c r="E20" t="n">
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Worked smoothly on Chrome with Freighter. Responsive layout renders cleanly on mobile viewports.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1255,17 +1231,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/04/2026 12:10:00</t>
+          <t>08/04/2026 12:49:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>Elena Rostova</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>elena.rostova.3d@creativepod.net</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1273,14 +1249,12 @@
           <t>GDRJPRJWJEOMJ6EPCLU44O2GY6MRNPWZYU2YMOS6VQYXQKZN2AXWH3PC</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
+      <c r="E21" t="n">
+        <v>5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>The Soroban smart contract handled our 70/30 creative revenue split with zero dust remaining in the vault.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1297,17 +1271,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/05/2026 02:05:00</t>
+          <t>08/05/2026 02:17:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>Oliver Campbell</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>v</t>
+          <t>oliver.campbell.dao@gmail.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1315,14 +1289,12 @@
           <t>GBMEPD3YJFDC7BM7V2NIELC6B4BRVIRFNK6XCUJMQEJ5YXHOHOSZ5GNF</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
+      <c r="E22" t="n">
+        <v>5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>Multi-sig proposal voting portal let our squad vote on new equity percentages without deploying a new contract.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1339,17 +1311,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/05/2026 16:42:00</t>
+          <t>08/05/2026 16:05:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>Sophia Torres</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>sophia.torres.qa@yahoo.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1357,14 +1329,12 @@
           <t>GCXDVRD3TTVZBSFWUHN7VB7W5SNDWXS5VULUQIS7O3BOEXRBTKF3JRA6</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
+      <c r="E23" t="n">
+        <v>4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>Clear error messaging when a wallet has insufficient balance. Intuitive user journey overall.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1381,17 +1351,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/06/2026 06:28:00</t>
+          <t>08/06/2026 06:45:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>Liam Chen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>liam.chen.infra@outlook.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1399,14 +1369,12 @@
           <t>GCPSN44M66YTYBWXINQFM2FJV5JUYX3HU4LRCV6ZDNAJ5NB5IYQMVWCK</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
+      <c r="E24" t="n">
+        <v>5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>The admin telemetry scanner let our team lead verify all 5 member trustlines before executing payout.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1423,17 +1391,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/06/2026 20:17:00</t>
+          <t>08/06/2026 20:31:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Amara Kowalski</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>amara.kowalski.sec@proton.me</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1441,14 +1409,12 @@
           <t>GCD72KGLFKHKE6YPCQ3GGL6COVJRCGDWWOJTHLBJZHAXMD4OWOQS3LDR</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
+      <c r="E25" t="n">
+        <v>5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Instant balance refresh from Horizon RPC showed my updated USDC balance right after settlement.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1470,12 +1436,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Marcus Dubois</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>marcus.dubois.fullstack@icloud.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1483,14 +1449,12 @@
           <t>GABQMF44C272GKITGYLEAWRCYWE6AOEI6FSOTDSH6DCBDFYSEAILAD7G</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E26" t="n">
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>Great platform for freelance dev pods. Looking forward to recurring retainer streams in Phase 2.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1507,17 +1471,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/08/2026 00:20:00</t>
+          <t>08/08/2026 00:09:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Chloe Nakamura</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>chloe.nakamura.defi@web3devs.io</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1525,14 +1489,12 @@
           <t>GAFAYTNW2LMHDGJJNJUDOTWUKHWBSOR7YGBED4S26WEMWD2TDRM37FLP</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
+      <c r="E27" t="n">
+        <v>5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>Tested equal 50/50 split on 5,000 USDC. Exactly 2,500 USDC arrived in each wallet instantaneously.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1549,17 +1511,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/08/2026 14:11:00</t>
+          <t>08/08/2026 14:31:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>j</t>
+          <t>Julian Al-Mansoor</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>julian.mansoor.dev@designcollective.co</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1567,14 +1529,12 @@
           <t>GB3VJZE6WYJDDK54CPAT5G4BHLATBUUK75LAFRR27F27BNAXEGFFHCDL</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
+      <c r="E28" t="n">
+        <v>5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>The transaction hash links directly to StellarExpert testnet, making auditing effortless for our client.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1591,17 +1551,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/09/2026 04:10:00</t>
+          <t>08/09/2026 04:49:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>Zoe Mendoza</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>zoe.mendoza.product@freelancehq.org</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1609,14 +1569,12 @@
           <t>GDUTEDQ5POUFJG4G3YTOIO77PUH677NSASGHAU26RZDZXEZVSH3JWVTR</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
+      <c r="E29" t="n">
+        <v>4</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>Slider controls for percentage shares are fluid and snap cleanly to whole basis points.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1633,17 +1591,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/09/2026 18:55:00</t>
+          <t>08/09/2026 18:23:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>Dante Becker</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>dante.becker.cloud@techsquad.dev</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1651,14 +1609,12 @@
           <t>GAI7DKRTI7PJSPAATREE7W6UD7IOZBLK64XWDUVKQGLFIGCG7GZVOBD5</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E30" t="n">
+        <v>5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>Gasless transaction execution via FeeBump envelopes makes onboarding Web2 clients completely friction-free.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1675,17 +1631,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/10/2026 08:05:00</t>
+          <t>08/10/2026 08:53:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>Nora Vargas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>nora.vargas.legal@creativepod.net</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1693,14 +1649,12 @@
           <t>GAVXLJLB57HWSLCSMNP5IYG2IPJ6R6ZYVYXHINYAEITNOBYIDEOTA2U4</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
+      <c r="E31" t="n">
+        <v>5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>The printable invoice receipt has all necessary cryptographic hashes for tax and corporate compliance.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1717,17 +1671,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/10/2026 22:29:00</t>
+          <t>08/10/2026 22:45:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>Gabriel Bautista</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>gabriel.bautista.contract@gmail.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1735,14 +1689,12 @@
           <t>GCD2H2T5TFOCLAZUUSMJVZMMKYKY4UEEZR56KVOA3RRPDSO37SM44YVZ</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E32" t="n">
+        <v>4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Fast contract deployment and invocation. Soroban's execution speeds on Stellar are impressive.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1759,17 +1711,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/11/2026 12:43:00</t>
+          <t>08/11/2026 12:23:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>Isla Lindqvist</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>isla.lindqvist.sprint@yahoo.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1777,14 +1729,12 @@
           <t>GCCB7RFR56PA6IV6DFP46WMJ2HP2EK3I2ZEG5NOMZJ4XQH233ICP63IJ</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
+      <c r="E33" t="n">
+        <v>5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>Tested a 4-person design sprint split. All payments settled simultaneously in a single atomic transaction.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1801,17 +1751,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/12/2026 02:34:00</t>
+          <t>08/12/2026 02:18:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Mateo Patel</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>mateo.patel.val@outlook.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1819,14 +1769,12 @@
           <t>GBUDHEBH5SR5WVC2AJIA6G7OTPTWPC7UMU3YCINAZR22LFWISX5PHJJL</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E34" t="n">
+        <v>5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>Accurate PHP and USD live currency valuation helped our distributed Manila-Singapore team align on pricing.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1843,17 +1791,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/12/2026 16:42:00</t>
+          <t>08/12/2026 16:11:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>Freja Hassan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>j</t>
+          <t>freja.hassan.ui@proton.me</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1861,14 +1809,12 @@
           <t>GCE4XUYCTBHBXWWZAWNQ5KBY5EKTY436LDCWSG5ON5VFYURNJFNRUDRR</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
+      <c r="E35" t="n">
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>Smooth interface. The toast alerts clearly communicated when the transaction was submitted and ledger-closed.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1885,17 +1831,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/13/2026 06:44:00</t>
+          <t>08/13/2026 06:47:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>Kai Moretti</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>_</t>
+          <t>kai.moretti.core@icloud.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1903,14 +1849,12 @@
           <t>GAOW7P6QWMXTU4KCXVDJ4I6CTZUFAAPJIS273UHYJCVXVTKHNQZF3F7I</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E36" t="n">
+        <v>5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>Zero remainder dust guarantee worked as advertised—the final stroop was routed cleanly to the designated member.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1927,17 +1871,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/13/2026 20:37:00</t>
+          <t>08/13/2026 20:34:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>Sienna Gomez</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>sienna.gomez.token@web3devs.io</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1945,14 +1889,12 @@
           <t>GAZC4YO7K3PAZSU55JTKCWSZZIC7ZSE63GIOGN3QQWRDIJVHKNUNXDOF</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
+      <c r="E37" t="n">
+        <v>5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>Freighter signing prompt displayed all contract arguments clearly. No hidden parameters.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1969,17 +1911,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/14/2026 10:12:00</t>
+          <t>08/14/2026 10:27:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Arjun Kim</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>arjun.kim.gov@designcollective.co</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1987,14 +1929,12 @@
           <t>GBOKCVNSTQ6XGEODDYBTNZ555AJZ7E3SM3X6CGHD2LCFI4M3V7LWPFQ3</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
+      <c r="E38" t="n">
+        <v>4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>j</t>
+          <t>The proposal voting portal with signature threshold calculation makes squad governance very transparent.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2011,17 +1951,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/15/2026 00:32:00</t>
+          <t>08/15/2026 00:51:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>Zara Schmidt</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>zara.schmidt.anim@freelancehq.org</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2029,14 +1969,12 @@
           <t>GCXXEBA3DUF3HDFYEZG2DG62BDZP7XLFQLXJIMWZQFJ27XDKPTZRKYAP</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E39" t="n">
+        <v>5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>Our 3D animation studio tested client billing and split. The client paid in 10 seconds without confusion.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2053,17 +1991,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/15/2026 14:45:00</t>
+          <t>08/15/2026 14:28:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>Ethan Tanaka</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>ethan.tanaka.rpc@techsquad.dev</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2071,14 +2009,12 @@
           <t>GBFBWF6NSBXG424KRNF4CG44HRGDTE33L2FMU7M3ORZE5K4UZ7HMMDVI</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
+      <c r="E40" t="n">
+        <v>5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>Horizon account balance query correctly identified native XLM vs SAC token balances in the header.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2095,17 +2031,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/16/2026 04:11:00</t>
+          <t>08/16/2026 04:47:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>Layla Ibrahim</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>layla.ibrahim.pulse@creativepod.net</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2113,14 +2049,12 @@
           <t>GARKPU7MJ2DV5PD6CJSH5WFEJAUJBHIWQ6PQ43FVHF7YRZVRTOI4E5LZ</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E41" t="n">
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>High quality visual telemetry. The live activity feed on the homepage shows real active transactions.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2137,17 +2071,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/16/2026 18:05:00</t>
+          <t>08/16/2026 18:42:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>Tariq Novak</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>tariq.novak.soroban@gmail.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2155,14 +2089,12 @@
           <t>GBBV53EUT6PFAEELEBI5V5UIRN5CJMQ3KTJ6WBKXLE7ZECHOZQ4KRWW6</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E42" t="n">
+        <v>5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>Tested contract invocations directly via StellarExpert explorer. Everything checked out 100%.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2179,17 +2111,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/17/2026 08:24:00</t>
+          <t>08/17/2026 08:31:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>Hanna Larsson</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>hanna.larsson.math@yahoo.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2197,14 +2129,12 @@
           <t>GDVKAJ2FHC6LZM37SB5M2ODUBK67CXW4EHMCRK246D37AQAHHQRJPRHU</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E43" t="n">
+        <v>5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>Excellent UX polish. The basis points input automatically validates that total sum equals 10,000 (100%).</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2221,17 +2151,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/17/2026 22:41:00</t>
+          <t>08/17/2026 22:35:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>Felix Diallo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>felix.diallo.billing@outlook.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2239,14 +2169,12 @@
           <t>GBVDPCYIK3MA4UZRCPZOBDBWNUOMU2GAWZ6MCPCNW6HRUUMDEB2ITKGH</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
+      <c r="E44" t="n">
+        <v>4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>Super intuitive invoice creator. Adding line items and assigning split percentages took under 1 minute.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2263,17 +2191,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/18/2026 12:53:00</t>
+          <t>08/18/2026 12:44:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Amina Popov</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>amina.popov.guild@proton.me</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2281,14 +2209,12 @@
           <t>GAXVNFS4OXHLXGPLIXE6QORTS2GWWCGCOZB5T5O3FN7LC7ZPWATW3Y34</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
+      <c r="E45" t="n">
+        <v>5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>Our translation guild used SplitSync for an ecosystem grant split. All 5 members received payouts instantly.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2305,17 +2231,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/19/2026 02:40:00</t>
+          <t>08/19/2026 02:47:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>j</t>
+          <t>Jonas Rossi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>jonas.rossi.audit@icloud.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2323,14 +2249,12 @@
           <t>GBVWKAIDAWDVJ4LGQRHNKY6223BWJ6SQKS75NBJGOAOAP53WFNUQDQ4X</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
+      <c r="E46" t="n">
+        <v>5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>The contract address and WASM hash are easily verifiable on-chain. Great transparency.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2347,17 +2271,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/19/2026 16:42:00</t>
+          <t>08/19/2026 16:40:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Camila Costa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>camila.costa.view@web3devs.io</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2365,14 +2289,12 @@
           <t>GBIJD7XXIT3F2HIGHEPUIBHUCNSYWJTWCZDLBNUS4Z7JNSF7DR3RLOS3</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E47" t="n">
+        <v>4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Very responsive layout on mobile viewport. Easy to monitor incoming settlements on the go.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2389,17 +2311,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/20/2026 06:21:00</t>
+          <t>08/20/2026 06:45:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>Kenji Olsen</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>j</t>
+          <t>kenji.olsen.relayer@designcollective.co</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2407,14 +2329,12 @@
           <t>GCZ7LEG4MVXTTYPEJS5OB5DV2KGMD2HYTAOAWZ76SPWRS7IK6DLBCVU5</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
+      <c r="E48" t="n">
+        <v>5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>The fee sponsorship relayer account handled transaction fees smoothly without delaying block inclusion.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2431,17 +2351,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/20/2026 20:30:00</t>
+          <t>08/20/2026 20:16:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>Fatima Mehta</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>fatima.mehta.collective@freelancehq.org</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2449,14 +2369,12 @@
           <t>GB4XQSR4J7Z7IHODNNL2KRGCNS2UBGLUTPLK5DDPO7VTZJTGFAYNPNKC</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="E49" t="n">
+        <v>5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>Best revenue splitting tool on Stellar. Makes running a decentralized developer collective practical.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2473,17 +2391,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/21/2026 10:30:00</t>
+          <t>08/21/2026 10:47:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>Rowan Chukwu</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>rowan.chukwu.nav@techsquad.dev</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2491,14 +2409,12 @@
           <t>GBDT3G24KIYBYXFC2FU4BJFAHP3AFPH6WSFZCC65WYRFAVU3DQFSM5BR</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
+      <c r="E50" t="n">
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>Clean navigation tabs. Tab 1 to 5 workflow makes logical sense from creation to administration.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2515,17 +2431,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/22/2026 00:42:00</t>
+          <t>08/22/2026 00:12:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Ananya Reyes</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>ananya.reyes.crypto@creativepod.net</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2533,14 +2449,12 @@
           <t>GAJZM4QLRJT6YPIGBCQV32FJDRSFFJT22I35J3SI42EHLEA7ENGJPTQN</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
+      <c r="E51" t="n">
+        <v>5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>10/10 experience testing the Soroban contract. Payout settled in under 3.5s with cryptographic proof.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
